--- a/narinakhre_products_upload (1).xlsx
+++ b/narinakhre_products_upload (1).xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\Documents\NariNakhre\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB1073A-C4CB-4F0F-B6FA-59D65B6A6F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -850,8 +856,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -888,13 +894,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -932,7 +946,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -966,6 +980,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1000,9 +1015,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1175,11 +1191,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1309,13 +1325,13 @@
         <v>236</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <v>250</v>
@@ -1387,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1407,13 +1423,13 @@
         <v>236</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <v>280</v>
@@ -1485,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1505,13 +1521,13 @@
         <v>236</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>250</v>
@@ -1583,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1603,13 +1619,13 @@
         <v>236</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <v>200</v>
@@ -1681,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1698,13 +1714,13 @@
         <v>237</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>120</v>
@@ -1776,7 +1792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1793,13 +1809,13 @@
         <v>237</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -1871,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1888,13 +1904,13 @@
         <v>238</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K8">
         <v>50</v>
@@ -1966,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1983,13 +1999,13 @@
         <v>238</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K9">
         <v>40</v>
@@ -2061,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2078,13 +2094,13 @@
         <v>238</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <v>30</v>
@@ -2156,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -2173,13 +2189,13 @@
         <v>236</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K11">
         <v>150</v>
@@ -2251,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -2268,13 +2284,13 @@
         <v>236</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <v>180</v>
@@ -2346,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -2363,13 +2379,13 @@
         <v>236</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K13">
         <v>150</v>
@@ -2441,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -2458,13 +2474,13 @@
         <v>236</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <v>150</v>
@@ -2536,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2553,13 +2569,13 @@
         <v>236</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K15">
         <v>750</v>
@@ -2631,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -2648,13 +2664,13 @@
         <v>236</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K16">
         <v>1200</v>
@@ -2726,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -2743,13 +2759,13 @@
         <v>236</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K17">
         <v>800</v>
@@ -2821,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -2838,13 +2854,13 @@
         <v>236</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K18">
         <v>350</v>
@@ -2916,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -2933,13 +2949,13 @@
         <v>236</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -3011,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -3028,13 +3044,13 @@
         <v>236</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20">
         <v>1000</v>
@@ -3106,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -3123,13 +3139,13 @@
         <v>236</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K21">
         <v>1000</v>
@@ -3201,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -3218,13 +3234,13 @@
         <v>236</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K22">
         <v>350</v>
@@ -3296,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -3313,13 +3329,13 @@
         <v>236</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23">
         <v>780</v>
@@ -3391,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -3408,13 +3424,13 @@
         <v>236</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K24">
         <v>600</v>
@@ -3486,7 +3502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -3506,13 +3522,13 @@
         <v>239</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K25">
         <v>650</v>
@@ -3584,7 +3600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -3604,13 +3620,13 @@
         <v>236</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K26">
         <v>280</v>
@@ -3682,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -3702,13 +3718,13 @@
         <v>239</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K27">
         <v>300</v>
@@ -3780,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:36">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -3800,13 +3816,13 @@
         <v>240</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K28">
         <v>150</v>
@@ -3878,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -3898,13 +3914,13 @@
         <v>239</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K29">
         <v>350</v>
@@ -3976,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -3996,13 +4012,13 @@
         <v>239</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K30">
         <v>350</v>
@@ -4074,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -4094,13 +4110,13 @@
         <v>239</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K31">
         <v>350</v>
@@ -4172,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -4192,13 +4208,13 @@
         <v>241</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -4270,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -4290,13 +4306,13 @@
         <v>237</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4368,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -4388,13 +4404,13 @@
         <v>239</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -4466,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -4486,13 +4502,13 @@
         <v>239</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K35">
         <v>350</v>
@@ -4564,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -4584,13 +4600,13 @@
         <v>239</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K36">
         <v>150</v>
@@ -4662,7 +4678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -4682,13 +4698,13 @@
         <v>242</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K37">
         <v>180</v>
@@ -4760,7 +4776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -4780,13 +4796,13 @@
         <v>242</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K38">
         <v>200</v>
@@ -4858,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -4878,13 +4894,13 @@
         <v>243</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K39">
         <v>165</v>
@@ -4956,7 +4972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -4976,13 +4992,13 @@
         <v>243</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K40">
         <v>190</v>
@@ -5054,7 +5070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>75</v>
       </c>
@@ -5074,13 +5090,13 @@
         <v>243</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41">
         <v>180</v>
@@ -5152,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -5172,13 +5188,13 @@
         <v>237</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K42">
         <v>30</v>
@@ -5250,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>77</v>
       </c>
@@ -5270,13 +5286,13 @@
         <v>239</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -5348,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -5368,13 +5384,13 @@
         <v>239</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K44">
         <v>650</v>
@@ -5446,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>79</v>
       </c>
@@ -5466,13 +5482,13 @@
         <v>239</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K45">
         <v>1200</v>
@@ -5544,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>80</v>
       </c>
@@ -5564,13 +5580,13 @@
         <v>239</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K46">
         <v>800</v>
@@ -5642,7 +5658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>81</v>
       </c>
@@ -5662,13 +5678,13 @@
         <v>239</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K47">
         <v>1100</v>
@@ -5740,7 +5756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>82</v>
       </c>
@@ -5760,13 +5776,13 @@
         <v>239</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K48">
         <v>650</v>
@@ -5838,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>83</v>
       </c>
@@ -5858,13 +5874,13 @@
         <v>244</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K49">
         <v>350</v>
@@ -5936,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -5956,13 +5972,13 @@
         <v>243</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K50">
         <v>300</v>
@@ -6034,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -6054,13 +6070,13 @@
         <v>243</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K51">
         <v>335</v>
@@ -6132,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>86</v>
       </c>
@@ -6152,13 +6168,13 @@
         <v>243</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K52">
         <v>400</v>
@@ -6230,7 +6246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>87</v>
       </c>
@@ -6250,13 +6266,13 @@
         <v>237</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K53">
         <v>100</v>
@@ -6328,7 +6344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>88</v>
       </c>
@@ -6348,13 +6364,13 @@
         <v>237</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K54">
         <v>100</v>
@@ -6426,7 +6442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>89</v>
       </c>
@@ -6446,13 +6462,13 @@
         <v>240</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K55">
         <v>180</v>
@@ -6524,7 +6540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:36">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>90</v>
       </c>
@@ -6544,13 +6560,13 @@
         <v>240</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -6622,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -6642,13 +6658,13 @@
         <v>240</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K57">
         <v>80</v>
@@ -6720,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:36">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>92</v>
       </c>
@@ -6740,13 +6756,13 @@
         <v>243</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K58">
         <v>650</v>
@@ -6818,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -6838,13 +6854,13 @@
         <v>243</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K59">
         <v>700</v>
@@ -6916,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -6936,13 +6952,13 @@
         <v>245</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K60">
         <v>200</v>
@@ -7014,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -7034,13 +7050,13 @@
         <v>245</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K61">
         <v>220</v>
@@ -7112,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>96</v>
       </c>
@@ -7132,13 +7148,13 @@
         <v>245</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K62">
         <v>150</v>
